--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486544_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486544_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.137</v>
+        <v>1.2121</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7728</v>
+        <v>1.8787</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6358</v>
+        <v>-0.6666</v>
       </c>
       <c r="G2" t="n">
         <v>-2.7934</v>
@@ -610,13 +610,13 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0402</v>
+        <v>2.1153</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5248</v>
+        <v>1.6307</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5154</v>
+        <v>0.4846</v>
       </c>
       <c r="V2" t="n">
         <v>1.8902</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>N. HOOVER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.647</v>
+        <v>0.8336</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0837</v>
+        <v>-0.2024</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4367</v>
+        <v>1.036</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7832</v>
+        <v>-2.8845</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.9952</v>
+        <v>-1.1649</v>
       </c>
       <c r="I3" t="n">
-        <v>1.212</v>
+        <v>-1.7196</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4777</v>
+        <v>-1.1313</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4348</v>
+        <v>-0.5991</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9125</v>
+        <v>-0.5323</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2608</v>
+        <v>-1.7532</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5604</v>
+        <v>-0.5659</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7004</v>
+        <v>-1.1873</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3099</v>
+        <v>1.0863</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5239</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.214</v>
+        <v>0.1574</v>
       </c>
       <c r="V3" t="n">
+        <v>1.1093</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.13</v>
-      </c>
       <c r="X3" t="n">
-        <v>-1.13</v>
+        <v>1.1093</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1924</v>
+        <v>0.8197</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9828</v>
+        <v>1.6101</v>
       </c>
       <c r="F4" t="n">
         <v>-0.7904</v>
@@ -766,10 +766,10 @@
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.423</v>
+        <v>0.2043</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9589</v>
+        <v>-0.3317</v>
       </c>
       <c r="U4" t="n">
         <v>0.536</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. MC MULLEN</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0159</v>
+        <v>0.7895</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1489</v>
+        <v>2.1954</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1648</v>
+        <v>-1.4059</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6256</v>
+        <v>-0.7832</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3593</v>
+        <v>-1.9952</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2662</v>
+        <v>1.212</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4811</v>
+        <v>1.4777</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5959</v>
+        <v>-0.4348</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1147</v>
+        <v>1.9125</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1444</v>
+        <v>-2.2608</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7635</v>
+        <v>-1.5604</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.381</v>
+        <v>-0.7004</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0023</v>
+        <v>-0.1673</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1102</v>
+        <v>-0.4122</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1079</v>
+        <v>0.2448</v>
       </c>
       <c r="V5" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. HOOVER</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0402</v>
+        <v>0.1403</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8297</v>
+        <v>0.3999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7894</v>
+        <v>-0.2596</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.8845</v>
+        <v>-1.9884</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1649</v>
+        <v>-2.3359</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7196</v>
+        <v>0.3475</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1313</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5991</v>
+        <v>-0.3436</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5323</v>
+        <v>1.1324</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7532</v>
+        <v>-2.7773</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5659</v>
+        <v>-1.9923</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1873</v>
+        <v>-0.7849</v>
       </c>
       <c r="P6" t="n">
         <v>1.5225</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>2.6101</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2125</v>
+        <v>0.0412</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3016</v>
+        <v>-0.4314</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0892</v>
+        <v>0.4726</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1093</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1093</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>N. MC MULLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1527</v>
+        <v>-0.7365</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0472</v>
+        <v>0.3666</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1055</v>
+        <v>-1.1031</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9884</v>
+        <v>-2.6256</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3359</v>
+        <v>-1.3593</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3475</v>
+        <v>-1.2662</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7887999999999999</v>
+        <v>-0.4811</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3436</v>
+        <v>-0.5959</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1324</v>
+        <v>0.1147</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7773</v>
+        <v>-2.1444</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.9923</v>
+        <v>-0.7635</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7849</v>
+        <v>-1.381</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5225</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6101</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2518</v>
+        <v>1.2816</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8784</v>
+        <v>1.3279</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6267</v>
+        <v>-0.0463</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.695</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9945000000000001</v>
+        <v>-1.6349</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3314</v>
+        <v>-1.2629</v>
       </c>
       <c r="F8" t="n">
-        <v>0.337</v>
+        <v>-0.3719</v>
       </c>
       <c r="G8" t="n">
         <v>-2.683</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1459</v>
+        <v>1.5054</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.0347</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1797</v>
+        <v>0.4708</v>
       </c>
       <c r="V8" t="n">
         <v>0.1952</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1804</v>
+        <v>-1.9569</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6006</v>
+        <v>-0.3771</v>
       </c>
       <c r="F9" t="n">
         <v>-1.5798</v>
@@ -1156,10 +1156,10 @@
         <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U9" t="n">
         <v>0.3425</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4244</v>
+        <v>-2.1662</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3898</v>
+        <v>-0.5016</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0345</v>
+        <v>-1.6646</v>
       </c>
       <c r="G10" t="n">
         <v>-4.3195</v>
@@ -1234,13 +1234,13 @@
         <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7657</v>
+        <v>1.0239</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2642</v>
+        <v>1.1524</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4985</v>
+        <v>-0.1286</v>
       </c>
       <c r="V10" t="n">
         <v>2.4345</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4693</v>
+        <v>-3.3491</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0044</v>
+        <v>-2.9717</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4649</v>
+        <v>-0.3774</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5857</v>
+        <v>-0.8637</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9251</v>
+        <v>1.0248</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6606</v>
+        <v>-1.8885</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7694</v>
+        <v>-0.2755</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4467</v>
+        <v>1.8067</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3227</v>
+        <v>-2.0822</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8162</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4783</v>
+        <v>-0.7819</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3379</v>
+        <v>0.1936</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.435</v>
+        <v>-0.87</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4486</v>
+        <v>0.0796</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1899</v>
+        <v>-0.1514</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2587</v>
+        <v>0.231</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>-0.3698</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6103</v>
+        <v>-3.5203</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2637</v>
+        <v>-2.2712</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3466</v>
+        <v>-1.2491</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8637</v>
+        <v>-2.5857</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0248</v>
+        <v>-1.9251</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8885</v>
+        <v>-0.6606</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2755</v>
+        <v>-0.7694</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8067</v>
+        <v>-0.4467</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0822</v>
+        <v>-0.3227</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-1.8162</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7819</v>
+        <v>-1.4783</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1936</v>
+        <v>-0.3379</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1816</v>
+        <v>-0.4996</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4434</v>
+        <v>-0.4566</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2618</v>
+        <v>-0.043</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3698</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.911300000000001</v>
+        <v>-9.568700000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.478599999999999</v>
+        <v>-1.1362</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.432600000000001</v>
+        <v>-8.432399999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-22.1132</v>
@@ -1438,16 +1438,16 @@
         <v>-14.34</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.773199999999999</v>
+        <v>-7.7732</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8620000000000001</v>
+        <v>0.862</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.8037999999999996</v>
+        <v>-0.8038000000000006</v>
       </c>
       <c r="L13" t="n">
-        <v>1.6657</v>
+        <v>1.665700000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-22.975</v>
@@ -1456,7 +1456,7 @@
         <v>-13.5362</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.4389</v>
+        <v>-9.438899999999999</v>
       </c>
       <c r="P13" t="n">
         <v>2.1751</v>
@@ -1468,16 +1468,16 @@
         <v>18.4881</v>
       </c>
       <c r="S13" t="n">
-        <v>6.483199999999999</v>
+        <v>6.8257</v>
       </c>
       <c r="T13" t="n">
-        <v>3.761499999999999</v>
+        <v>4.103800000000001</v>
       </c>
       <c r="U13" t="n">
         <v>2.7218</v>
       </c>
       <c r="V13" t="n">
-        <v>3.5438</v>
+        <v>3.543799999999999</v>
       </c>
       <c r="W13" t="n">
         <v>10.2112</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.2807</v>
+        <v>9.809900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>6.8835</v>
+        <v>7.3306</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3971</v>
+        <v>2.4794</v>
       </c>
       <c r="G14" t="n">
         <v>6.8479</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1506</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.548</v>
+        <v>-0.1009</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6985</v>
+        <v>0.7808</v>
       </c>
       <c r="V14" t="n">
         <v>2.0647</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>M. JACKSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7278</v>
+        <v>5.9623</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1814</v>
+        <v>4.5952</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5465</v>
+        <v>1.3671</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5582</v>
+        <v>3.0941</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7342</v>
+        <v>1.2135</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8239</v>
+        <v>1.8806</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7893</v>
+        <v>3.5421</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5216</v>
+        <v>1.2838</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2677</v>
+        <v>2.2583</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7688</v>
+        <v>-0.448</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2127</v>
+        <v>-0.0703</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5562</v>
+        <v>-0.3778</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8445</v>
+        <v>-0.0018</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4817</v>
+        <v>-0.0769</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3628</v>
+        <v>0.0751</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7602</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>2.0854</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. JACKSON</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.356</v>
+        <v>4.532</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5952</v>
+        <v>3.1755</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7609</v>
+        <v>1.3564</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0941</v>
+        <v>3.5582</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2135</v>
+        <v>2.7342</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8806</v>
+        <v>0.8239</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5421</v>
+        <v>2.7893</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2838</v>
+        <v>2.5216</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2583</v>
+        <v>0.2677</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.448</v>
+        <v>0.7688</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0703</v>
+        <v>0.2127</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3778</v>
+        <v>0.5562</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7401</v>
+        <v>-0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6081</v>
+        <v>0.6486</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0769</v>
+        <v>0.4759</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5312</v>
+        <v>0.1727</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>0.7602</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>2.0854</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.155</v>
+        <v>2.6328</v>
       </c>
       <c r="E17" t="n">
         <v>4.1827</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0278</v>
+        <v>-1.5499</v>
       </c>
       <c r="G17" t="n">
         <v>6.953</v>
@@ -1780,13 +1780,13 @@
         <v>2.8276</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3205</v>
+        <v>-0.8427</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2824</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0382</v>
+        <v>-0.5603</v>
       </c>
       <c r="V17" t="n">
         <v>-2.8249</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>J. ZIDEK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6574</v>
+        <v>1.836</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1125</v>
+        <v>-0.4125</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7699</v>
+        <v>2.2486</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8046</v>
+        <v>-0.022</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0213</v>
+        <v>1.3351</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7833</v>
+        <v>-1.357</v>
       </c>
       <c r="J18" t="n">
-        <v>0.093</v>
+        <v>0.8547</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0547</v>
+        <v>1.3869</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0382</v>
+        <v>-0.5323</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7116</v>
+        <v>-0.8767</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0335</v>
+        <v>-0.0519</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7451</v>
+        <v>-0.8248</v>
       </c>
       <c r="P18" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.435</v>
+        <v>2.6101</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4178</v>
+        <v>-0.2295</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2055</v>
+        <v>-0.3749</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6233</v>
+        <v>0.1454</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ZIDEK</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6697</v>
+        <v>1.5649</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8596</v>
+        <v>-0.1125</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5292</v>
+        <v>1.6774</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.022</v>
+        <v>0.8046</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3351</v>
+        <v>0.0213</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.357</v>
+        <v>0.7833</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8547</v>
+        <v>0.093</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3869</v>
+        <v>0.0547</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5323</v>
+        <v>0.0382</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8767</v>
+        <v>0.7116</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0519</v>
+        <v>-0.0335</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8248</v>
+        <v>0.7451</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6101</v>
+        <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3959</v>
+        <v>0.3254</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.822</v>
+        <v>-0.2055</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5739</v>
+        <v>0.5308</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ALONSO RUIZ</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0436</v>
+        <v>-0.7214</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5122</v>
+        <v>-0.9041</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5558</v>
+        <v>0.1827</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5178</v>
+        <v>0.2574</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4835</v>
+        <v>1.6544</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0343</v>
+        <v>-1.3969</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6867</v>
+        <v>0.6671</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0365</v>
+        <v>1.2592</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6502</v>
+        <v>-0.5921</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1689</v>
+        <v>-0.4097</v>
       </c>
       <c r="N20" t="n">
-        <v>0.447</v>
+        <v>0.3951</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.616</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P20" t="n">
+        <v>0.2175</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.305</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.5225</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-1.3916</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.4614</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.9301</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>-0.2569</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>-0.2569</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-1.3045</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-0.1745</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. CZERAPOWICZ</t>
+          <t>A. ALONSO RUIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.047</v>
+        <v>-0.982</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0078</v>
+        <v>0.5122</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0392</v>
+        <v>-1.4942</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5866</v>
+        <v>0.5178</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0214</v>
+        <v>0.4835</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.608</v>
+        <v>0.0343</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2478</v>
+        <v>0.6867</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5538</v>
+        <v>0.0365</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8016</v>
+        <v>0.6502</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3388</v>
+        <v>-0.1689</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5324</v>
+        <v>0.447</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1936</v>
+        <v>-0.616</v>
       </c>
       <c r="P21" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2346</v>
+        <v>-0.1953</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1971</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0375</v>
+        <v>-0.1953</v>
       </c>
       <c r="V21" t="n">
+        <v>-1.3045</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.1745</v>
+      </c>
+      <c r="X21" t="n">
         <v>-1.13</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-0.7395</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-0.3904</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>C. CZERAPOWICZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6385</v>
+        <v>-1.4798</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1276</v>
+        <v>-1.343</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5109</v>
+        <v>-0.1368</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2574</v>
+        <v>-0.5866</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6544</v>
+        <v>0.0214</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3969</v>
+        <v>-0.608</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6671</v>
+        <v>-0.2478</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2592</v>
+        <v>0.5538</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5921</v>
+        <v>-0.8016</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4097</v>
+        <v>-0.3388</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3951</v>
+        <v>-0.5324</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8048999999999999</v>
+        <v>0.1936</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3087</v>
+        <v>-0.1983</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.1382</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.6237</v>
+        <v>-0.0601</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9491</v>
+        <v>-2.2863</v>
       </c>
       <c r="E23" t="n">
         <v>-1.1244</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8247</v>
+        <v>-1.1619</v>
       </c>
       <c r="G23" t="n">
         <v>1.0669</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2982</v>
+        <v>-0.6354</v>
       </c>
       <c r="T23" t="n">
         <v>-0.548</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7502</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7602</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5317</v>
+        <v>-3.339</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2188</v>
+        <v>-4.9953</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6872</v>
+        <v>1.6563</v>
       </c>
       <c r="G24" t="n">
         <v>1.8099</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8822</v>
+        <v>-0.6895</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6165</v>
+        <v>-0.3929</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2657</v>
+        <v>-0.2965</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5443</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7254</v>
+        <v>-4.638</v>
       </c>
       <c r="E25" t="n">
         <v>-2.2765</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4489</v>
+        <v>-2.3616</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1878</v>
@@ -2404,13 +2404,13 @@
         <v>1.5225</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0601</v>
+        <v>-0.9728</v>
       </c>
       <c r="T25" t="n">
         <v>-0.6165</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4437</v>
+        <v>-0.3563</v>
       </c>
       <c r="V25" t="n">
         <v>-1.695</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>9.911299999999997</v>
+        <v>12.8914</v>
       </c>
       <c r="E26" t="n">
-        <v>8.627799999999993</v>
+        <v>8.6279</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2835</v>
+        <v>4.2635</v>
       </c>
       <c r="G26" t="n">
         <v>22.1134</v>
@@ -2461,7 +2461,7 @@
         <v>13.5362</v>
       </c>
       <c r="L26" t="n">
-        <v>9.438699999999999</v>
+        <v>9.438699999999997</v>
       </c>
       <c r="M26" t="n">
         <v>-0.8618999999999999</v>
@@ -2482,13 +2482,13 @@
         <v>16.3129</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.483099999999999</v>
+        <v>-3.503</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.722</v>
+        <v>-2.7217</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.761399999999999</v>
+        <v>-0.7811999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-3.5438</v>
